--- a/public/documents/pieces-reponse-1/R1-p81-articles-unite.xlsx
+++ b/public/documents/pieces-reponse-1/R1-p81-articles-unite.xlsx
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -4790,14 +4790,14 @@
       <c r="B36" s="4" t="inlineStr"/>
       <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="n">
-        <v>2779</v>
+        <v>2759</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>14,5 %</t>
+          <t>13,9 %</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
@@ -4816,14 +4816,14 @@
       <c r="B37" s="8" t="inlineStr"/>
       <c r="C37" s="8" t="inlineStr"/>
       <c r="D37" s="8" t="n">
-        <v>9615</v>
+        <v>9595</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>1242</v>
+        <v>1222</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>12,9 %</t>
+          <t>12,7 %</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr"/>
